--- a/backtest_runs/20260410_193731/by_symbol/HAEL/HAEL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HAEL/HAEL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>100000</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>102763.36</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>102763.36</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>110650.45</v>
@@ -1185,7 +1185,7 @@
         <v>-345.4199999999926</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>116580.16</v>
@@ -1277,7 +1277,7 @@
         <v>-1727.100000000004</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>114853.06</v>
@@ -1369,7 +1369,7 @@
         <v>-6850.829999999987</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>108002.23</v>
@@ -1415,7 +1415,7 @@
         <v>-8232.510000000009</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>99769.72000000002</v>
@@ -1507,7 +1507,7 @@
         <v>-3281.490000000002</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>96488.23000000001</v>
@@ -1599,7 +1599,7 @@
         <v>-3511.770000000017</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>92976.45999999999</v>
